--- a/docs/03_test/WhiteBoxTest.xlsx
+++ b/docs/03_test/WhiteBoxTest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\WEBアプリ開発演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4112A921-C082-450E-B602-B264D63A6962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657BAEB7-F2BA-4158-89BA-C9024AE12607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{932F9C55-0850-4CD1-9477-4415B254A7A2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{932F9C55-0850-4CD1-9477-4415B254A7A2}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト実施概要" sheetId="3" r:id="rId1"/>
@@ -1006,7 +1006,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1064,18 +1064,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1106,41 +1094,44 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1546,7 +1537,7 @@
       </c>
     </row>
     <row r="3" spans="2:2" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="29" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1760,11 +1751,11 @@
     <col min="1" max="1" width="3.83203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.75" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="7" width="74.1640625" customWidth="1"/>
-    <col min="8" max="8" width="11.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1793,12 +1784,12 @@
       <c r="H1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2">
+      <c r="A2" s="24">
         <v>1</v>
       </c>
       <c r="B2" s="18">
@@ -1822,12 +1813,12 @@
       <c r="H2" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="24">
         <v>2</v>
       </c>
       <c r="B3" s="18">
@@ -1851,67 +1842,67 @@
       <c r="H3" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="34">
+      <c r="A4" s="32">
         <v>3</v>
       </c>
-      <c r="B4" s="41">
+      <c r="B4" s="30">
         <v>46169</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="35" t="s">
         <v>41</v>
       </c>
       <c r="G4" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="I4" s="33" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="34"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
       <c r="G5" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="42"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="33"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="34"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
       <c r="G6" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="42"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="33"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="2">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
       <c r="B7" s="18">
@@ -1935,12 +1926,12 @@
       <c r="H7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="2">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
       <c r="B8" s="18">
@@ -1964,12 +1955,12 @@
       <c r="H8" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="2">
+      <c r="A9" s="24">
         <v>6</v>
       </c>
       <c r="B9" s="18">
@@ -1993,12 +1984,12 @@
       <c r="H9" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="2">
+      <c r="A10" s="24">
         <v>7</v>
       </c>
       <c r="B10" s="18">
@@ -2022,36 +2013,36 @@
       <c r="H10" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="2">
+      <c r="A11" s="25">
         <v>8</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="26">
         <v>46169</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2088,36 +2079,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="28">
+      <c r="A2" s="24">
         <v>1</v>
       </c>
       <c r="B2" s="18">
@@ -2146,7 +2137,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="28">
+      <c r="A3" s="24">
         <v>2</v>
       </c>
       <c r="B3" s="18">
@@ -2175,7 +2166,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="28">
+      <c r="A4" s="24">
         <v>3</v>
       </c>
       <c r="B4" s="18">
@@ -2204,62 +2195,62 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="35">
+      <c r="A5" s="32">
         <v>4</v>
       </c>
       <c r="B5" s="36">
         <v>46169</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="40" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="35" t="s">
         <v>71</v>
       </c>
       <c r="G5" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="H5" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="38" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="35"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="38"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="39"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
       <c r="G6" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="35"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="38"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="39"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
       <c r="G7" t="s">
         <v>70</v>
       </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="28">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
       <c r="B8" s="18">
@@ -2288,19 +2279,19 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="29">
+      <c r="A9" s="25">
         <v>6</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="26">
         <v>46169</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="26" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="27" t="s">
         <v>92</v>
       </c>
       <c r="F9" s="10" t="s">
@@ -2309,7 +2300,7 @@
       <c r="G9" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="28" t="s">
         <v>88</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -2349,91 +2340,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="35">
+      <c r="A2" s="32">
         <v>1</v>
       </c>
       <c r="B2" s="36">
         <v>46169</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="40" t="s">
         <v>86</v>
       </c>
       <c r="G2" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="38" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="35"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="40"/>
       <c r="G3" t="s">
         <v>84</v>
       </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="35"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="34"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="40"/>
       <c r="G4" t="s">
         <v>85</v>
       </c>
-      <c r="H4" s="34"/>
-      <c r="I4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="28">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
       <c r="B5" s="18">
@@ -2462,7 +2453,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="28">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
       <c r="B6" s="18">
@@ -2491,7 +2482,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="28">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
       <c r="B7" s="18">
@@ -2520,7 +2511,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="28">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
       <c r="B8" s="18">
@@ -2549,10 +2540,10 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="29">
+      <c r="A9" s="25">
         <v>6</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="26">
         <v>46169</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -2561,7 +2552,7 @@
       <c r="D9" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="27" t="s">
         <v>92</v>
       </c>
       <c r="F9" s="10" t="s">
@@ -2570,7 +2561,7 @@
       <c r="G9" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="28" t="s">
         <v>88</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -2600,34 +2591,34 @@
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="38"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="39"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="38"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="39"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="34"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="38"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="39"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="H18" s="2"/>
